--- a/aa/xlsx/healthcheck-map.xlsx
+++ b/aa/xlsx/healthcheck-map.xlsx
@@ -430,7 +430,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IF-005</t>
+          <t>H0</t>
         </is>
       </c>
     </row>
@@ -442,7 +442,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IF-005</t>
+          <t>H0</t>
         </is>
       </c>
     </row>
